--- a/product_upload/packages/42/file.xlsx
+++ b/product_upload/packages/42/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>NICOTINELL TTS-10</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-249B0C57CDFF</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1036,6 +1046,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>LEPONEX 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-62BAC0168123</t>
         </is>
       </c>
@@ -1059,7 +1074,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1218,6 +1233,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>SILOMES 200 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-B8B7B4080C06</t>
         </is>
       </c>
@@ -1241,7 +1261,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1396,6 +1416,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DERMALSTYLE forte Lidocaine</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-565A51D63C8D</t>
         </is>
       </c>
@@ -1419,7 +1444,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1574,6 +1599,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>DERMALSTYLE smile Lidocaine</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-831B1D3119F9</t>
         </is>
       </c>
@@ -1597,7 +1627,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1768,6 +1798,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Amgevita 40 mg per 0.8 ml syringe</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-C5E45D647834</t>
         </is>
       </c>
@@ -1791,7 +1826,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1958,6 +1993,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Amgevita 40 mg per 0.8 ml Pen</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-79C783BE589A</t>
         </is>
       </c>
@@ -1981,7 +2021,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2148,6 +2188,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>ANGIRAM</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-EF115EDE4F97</t>
         </is>
       </c>
@@ -2171,7 +2216,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2342,6 +2387,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>ANGIRAM</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-331B1DE0B888</t>
         </is>
       </c>
@@ -2365,7 +2415,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2528,6 +2578,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>CAL-C-VITA EFFERVESCENT</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-AB6E91BE54DF</t>
         </is>
       </c>
@@ -2551,7 +2606,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2718,6 +2773,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>MILORA HCT</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-2BC3F1024364</t>
         </is>
       </c>
@@ -2741,7 +2801,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2908,6 +2968,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>MILORA HCT</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-CA1BA9C83D14</t>
         </is>
       </c>
@@ -2931,7 +2996,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3098,6 +3163,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>MILORA HCT</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-92EC6A34D6B9</t>
         </is>
       </c>
@@ -3121,7 +3191,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3284,6 +3354,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>VERTEX</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-DD09A977109D</t>
         </is>
       </c>
@@ -3307,7 +3382,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3478,6 +3553,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>VERTEX</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-61B177572531</t>
         </is>
       </c>
@@ -3501,7 +3581,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3664,6 +3744,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>YOCAIR 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-6E674034D652</t>
         </is>
       </c>
@@ -3687,7 +3772,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3854,6 +3939,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>DAPOX 30MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-2A1D33466EF9</t>
         </is>
       </c>
@@ -3877,7 +3967,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4048,6 +4138,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>DAPOX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-C2FE8D577D9A</t>
         </is>
       </c>
@@ -4071,7 +4166,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4226,6 +4321,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>NEUPRO 2 mg/24 hrs Transdermal Patches</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-9647089A1898</t>
         </is>
       </c>
@@ -4249,7 +4349,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4420,6 +4520,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>KOZAMOD 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-2D5C31519863</t>
         </is>
       </c>
@@ -4443,7 +4548,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4610,6 +4715,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>TACROZ 0.03% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-CC94798369AE</t>
         </is>
       </c>
@@ -4633,7 +4743,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4796,6 +4906,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>NITYR 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-3AB22D911866</t>
         </is>
       </c>
@@ -4819,7 +4934,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4990,6 +5105,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>NICOTINELL TTS-20</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-D6C4F84EA98B</t>
         </is>
       </c>
@@ -5013,7 +5133,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5182,6 +5302,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>LEPONEX 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-237A56FA1EC0</t>
         </is>
       </c>
@@ -5205,7 +5330,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5364,6 +5489,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>APRELEX 20MCG/ML INHALATION SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-53E45257032E</t>
         </is>
       </c>
@@ -5387,7 +5517,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5554,6 +5684,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>ADANCOR 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-1DEE0007A83D</t>
         </is>
       </c>
@@ -5577,7 +5712,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5740,6 +5875,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>ISENTRESS 600MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-5034591D8083</t>
         </is>
       </c>
@@ -5763,7 +5903,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5932,6 +6072,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>SOLIAN 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-C68110FC27F1</t>
         </is>
       </c>
@@ -5955,7 +6100,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6118,6 +6263,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>CO-OLMEPRESS 20 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-77EC3C13CD31</t>
         </is>
       </c>
@@ -6141,7 +6291,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6308,6 +6458,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>FLUSORT 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-75A8E82CC163</t>
         </is>
       </c>
@@ -6331,7 +6486,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6490,6 +6645,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>NITYR 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-F25DC63A40A2</t>
         </is>
       </c>
@@ -6513,7 +6673,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6680,6 +6840,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>NICOTINELL TTS-30</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-06B26C54B650</t>
         </is>
       </c>
@@ -6703,7 +6868,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6866,6 +7031,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>OLMIDIP 20/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-84CC214A4FAC</t>
         </is>
       </c>
@@ -6889,7 +7059,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7052,6 +7222,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>OLMIDIP 40/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-21F69A2688D1</t>
         </is>
       </c>
@@ -7075,7 +7250,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7238,6 +7413,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>OLMIDIP 40/10 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-D291F47ED7A8</t>
         </is>
       </c>
@@ -7261,7 +7441,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7420,6 +7600,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>DAMESTA 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-D0C00F0210D9</t>
         </is>
       </c>
@@ -7443,7 +7628,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7602,6 +7787,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>DAMESTA  20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-61584D4AB568</t>
         </is>
       </c>
@@ -7625,7 +7815,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7792,6 +7982,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>LAZURE 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-B7BEA266724A</t>
         </is>
       </c>
@@ -7815,7 +8010,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7982,6 +8177,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>LAZURE 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-EEBEFD60C64F</t>
         </is>
       </c>
@@ -8005,7 +8205,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8176,6 +8376,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>LAZURE 200MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-C67BE2794F73</t>
         </is>
       </c>
@@ -8199,7 +8404,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8362,6 +8567,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>PIRAMYL-MET 2/500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-EC91F89D1FE2</t>
         </is>
       </c>
@@ -8385,7 +8595,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8548,6 +8758,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>LIFANCE 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-7314CB47749E</t>
         </is>
       </c>
@@ -8571,7 +8786,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8726,6 +8941,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>LIFANCE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-BF92C81C2256</t>
         </is>
       </c>
@@ -8749,7 +8969,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8920,6 +9140,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>LEJAM 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-B717AAE38EF9</t>
         </is>
       </c>
@@ -8943,7 +9168,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9110,6 +9335,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>LEJAM 60MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-0C1611A94115</t>
         </is>
       </c>
@@ -9133,7 +9363,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9304,6 +9534,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ABSTRAL 100MCG SUBLINGUAL TABLET</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-8621A674FCFC</t>
         </is>
       </c>
@@ -9327,7 +9562,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9486,6 +9721,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>PAQUIX 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-96FAFBFF5B93</t>
         </is>
       </c>
@@ -9509,7 +9749,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9680,6 +9920,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>PAQUIX 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-9998068FDD4B</t>
         </is>
       </c>
@@ -9703,7 +9948,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9870,6 +10115,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>PAQUIX 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-06E5D14111A1</t>
         </is>
       </c>
@@ -9893,7 +10143,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10064,6 +10314,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>ABSTRAL 200MCG SUBLINGUAL TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-42844CDF9B8C</t>
         </is>
       </c>
@@ -10087,7 +10342,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10258,6 +10513,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>LANOXIN 0.125MG TAB</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-09BB7EDD4110</t>
         </is>
       </c>
@@ -10281,7 +10541,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10444,6 +10704,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>LANOXIN 0.25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-C13D5C280F3D</t>
         </is>
       </c>
@@ -10467,7 +10732,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10638,6 +10903,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>IMURAN</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-2387F7EC1B7D</t>
         </is>
       </c>
@@ -10661,7 +10931,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10822,6 +11092,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>RECOMBIVAX HB</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-98CBC548A94A</t>
         </is>
       </c>
@@ -10845,7 +11120,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11002,6 +11277,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>RECOMBIVAX HB</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-1FD5A71F5AE5</t>
         </is>
       </c>
@@ -11025,7 +11305,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11192,6 +11472,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>LIPANTHYL 145MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-B00D2310E9F9</t>
         </is>
       </c>
@@ -11215,7 +11500,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11374,6 +11659,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>LINDEC 600 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-6288B38896BA</t>
         </is>
       </c>
@@ -11397,7 +11687,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11564,6 +11854,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>NIZORAL SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-8E043531D650</t>
         </is>
       </c>
@@ -11587,7 +11882,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11754,6 +12049,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Cuprior</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-4158AD9B369B</t>
         </is>
       </c>
@@ -11777,7 +12077,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11932,6 +12232,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>NEUPRO 8 mg/24 hrs Transdermal Patches</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-966F31A5708D</t>
         </is>
       </c>
@@ -11955,7 +12260,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12118,6 +12423,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>GASTROGRAFIN 76-ORAL AQUEOUS SOLN.</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-94A36777FBF5</t>
         </is>
       </c>
@@ -12141,7 +12451,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12300,6 +12610,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>NEUPRO 6 mg/24 hrs Transdermal Patches</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-F8A3035E7BEA</t>
         </is>
       </c>
@@ -12323,7 +12638,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12486,6 +12801,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>VIRONTA</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-B7D475986A82</t>
         </is>
       </c>
@@ -12509,7 +12829,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12668,6 +12988,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>VIRONTA</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-3B439797BF25</t>
         </is>
       </c>
@@ -12691,7 +13016,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12854,6 +13179,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>VIRONTA</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-2C7618EFD1C1</t>
         </is>
       </c>
@@ -12877,7 +13207,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13036,6 +13366,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>PEDEXA</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-C3F49E511348</t>
         </is>
       </c>
@@ -13059,7 +13394,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13222,6 +13557,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>TYRA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-DF6721FF6C5F</t>
         </is>
       </c>
@@ -13245,7 +13585,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13404,6 +13744,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>PRAVAFEN 40/160 mg</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-90ED203245BE</t>
         </is>
       </c>
@@ -13427,7 +13772,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13586,6 +13931,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Kavira</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-932EBE146DB9</t>
         </is>
       </c>
@@ -13609,7 +13959,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13772,6 +14122,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Kavira</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-2ABA8CD375F4</t>
         </is>
       </c>
@@ -13795,7 +14150,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13966,6 +14321,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>DILATREND 25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-EA35673EB312</t>
         </is>
       </c>
@@ -13989,7 +14349,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14158,6 +14518,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>LIPANTHYL 200MG MICRONISED CAPS</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-F4B63CF4727E</t>
         </is>
       </c>
@@ -14181,7 +14546,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14348,6 +14713,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>CYCLOGEST 200MG PESSARIES</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-0E031B11ADBF</t>
         </is>
       </c>
@@ -14371,7 +14741,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14526,6 +14896,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>PecFent 400 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-C0B0B03A224F</t>
         </is>
       </c>
@@ -14549,7 +14924,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14722,6 +15097,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>ATACAND PLUS TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-26BFFA77048C</t>
         </is>
       </c>
@@ -14745,7 +15125,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14918,6 +15298,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>NEXIUM 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-74087A5F51D7</t>
         </is>
       </c>
@@ -14941,7 +15326,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15100,6 +15485,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>RAPAMUNE 1 MG Coated tablet</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-E50B473B4E1E</t>
         </is>
       </c>
@@ -15123,7 +15513,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15282,6 +15672,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>TWINZOL EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-BB38FF3E2A76</t>
         </is>
       </c>
@@ -15305,7 +15700,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15464,6 +15859,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>XIIDRA 50 MG/ML EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-DEB925A0A087</t>
         </is>
       </c>
@@ -15487,7 +15887,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15660,6 +16060,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>BOSENTOR 62.5 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-9BE08293C93E</t>
         </is>
       </c>
@@ -15683,7 +16088,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15844,6 +16249,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>PEEVO</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-352D02783775</t>
         </is>
       </c>
@@ -15867,7 +16277,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16018,6 +16428,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t xml:space="preserve">NEURITAM </t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D9184918F6B5</t>
         </is>
       </c>
@@ -16041,7 +16456,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16200,6 +16615,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t xml:space="preserve">NEURITAM </t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-4E520497CC52</t>
         </is>
       </c>
@@ -16223,7 +16643,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16390,6 +16810,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>MILORA HCT</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-E97A0402DE61</t>
         </is>
       </c>
@@ -16413,7 +16838,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16580,6 +17005,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Zolinda Oral Solution</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-0D3FD1B143CC</t>
         </is>
       </c>
@@ -16603,7 +17033,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16766,6 +17196,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t xml:space="preserve">LORBRENA </t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-FBCA6FE34B82</t>
         </is>
       </c>
@@ -16789,7 +17224,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16952,6 +17387,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Carglumic Acid Waymade </t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-22643AD301BB</t>
         </is>
       </c>
@@ -16975,7 +17415,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17142,6 +17582,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Carglumic Acid Waymade </t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-9BD0F3984642</t>
         </is>
       </c>
@@ -17165,7 +17610,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17332,6 +17777,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t xml:space="preserve">LORBRENA </t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-99842B707961</t>
         </is>
       </c>
@@ -17355,7 +17805,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17526,6 +17976,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Metolina </t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-DA3956248797</t>
         </is>
       </c>
@@ -17549,7 +18004,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17722,6 +18177,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>DEXILANT 60 mg</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-7C08747BF427</t>
         </is>
       </c>
@@ -17745,7 +18205,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17914,6 +18374,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>ADOL EXTRA CAPLETS</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-36C5F11A42F1</t>
         </is>
       </c>
@@ -17937,7 +18402,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18104,6 +18569,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>DILATREND 6.25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-E406068AAC06</t>
         </is>
       </c>
@@ -18127,7 +18597,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18300,6 +18770,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>KLACID 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-98BDA74570A6</t>
         </is>
       </c>
@@ -18323,7 +18798,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18490,6 +18965,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>CYCLOGEST 400MG PESSARIES</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-27D088C9FF6E</t>
         </is>
       </c>
@@ -18513,7 +18993,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18676,6 +19156,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>PecFent 400 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-B4C2D10E5F7A</t>
         </is>
       </c>
@@ -18699,7 +19184,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18868,6 +19353,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>NEXIUM 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-3F84918F3A2B</t>
         </is>
       </c>
@@ -18891,7 +19381,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19050,6 +19540,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Hyalo4 Plus</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-730FF857ACCE</t>
         </is>
       </c>
@@ -19073,7 +19568,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19246,6 +19741,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>BOSENTOR 125 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-C60655F953DE</t>
         </is>
       </c>
@@ -19269,7 +19769,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19431,6 +19931,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>INTRAROSA</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-B9D46FCF5D7D</t>
         </is>
@@ -19447,7 +19952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19493,100 +19998,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19618,7 +20128,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19633,92 +20143,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-47341</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>333.76</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>386</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19750,7 +20265,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19765,92 +20280,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-26396</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>418.72</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>387</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19882,7 +20402,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19897,92 +20417,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-89472</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>58.6</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>388</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20014,7 +20539,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20029,92 +20554,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-48752</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>115.87</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>389</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20146,7 +20676,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20161,92 +20691,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-24463</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>290.45</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>390</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20278,7 +20813,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20293,92 +20828,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-95246</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>345.07</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>391</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20410,7 +20950,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20425,92 +20965,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-37947</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>21.66</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>392</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20542,7 +21087,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20557,92 +21102,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-19313</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>477.68</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>393</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20674,7 +21224,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20689,92 +21239,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-58484</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>69.06</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>394</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20806,7 +21361,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20821,92 +21376,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-79260</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>227.67</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>395</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20938,7 +21498,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20953,92 +21513,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-87315</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>472.17</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>396</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21055,7 +21620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21161,6 +21726,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21196,7 +21771,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21261,6 +21836,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-5C202FCD1769</t>
         </is>
@@ -21297,7 +21882,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21362,6 +21947,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1888F7186BDF</t>
         </is>
@@ -21398,7 +21993,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21463,6 +22058,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-1B1DC0DFC601</t>
         </is>
@@ -21499,7 +22104,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21564,6 +22169,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-72DBF593D70C</t>
         </is>
@@ -21600,7 +22215,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21665,6 +22280,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-39B4B6256B28</t>
         </is>
@@ -21701,7 +22326,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21766,6 +22391,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-EAFEA49F01CD</t>
         </is>
@@ -21802,7 +22437,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21867,6 +22502,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-077D984A300A</t>
         </is>
@@ -21903,7 +22548,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21968,6 +22613,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-7C9AD9EB502A</t>
         </is>
@@ -22004,7 +22659,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22069,6 +22724,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-55FE4599DB71</t>
         </is>
@@ -22105,7 +22770,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22170,6 +22835,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-BEED988B89B8</t>
         </is>
@@ -22206,7 +22881,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22271,6 +22946,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-AADCB4EA6DAF</t>
         </is>
@@ -22307,7 +22992,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22372,6 +23057,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-E221A0B0F398</t>
         </is>
@@ -22408,7 +23103,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22473,6 +23168,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-89330BCB3D85</t>
         </is>
@@ -22509,7 +23214,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22574,6 +23279,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-E57A416F445D</t>
         </is>
@@ -22610,7 +23325,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22675,6 +23390,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-1E0489938352</t>
         </is>
@@ -22711,7 +23436,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22776,6 +23501,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-FBE2215685C5</t>
         </is>
@@ -22812,7 +23547,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22877,6 +23612,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-46801301C804</t>
         </is>
@@ -22913,7 +23658,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22978,6 +23723,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-1520CA1C9DF9</t>
         </is>
@@ -23014,7 +23769,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23079,6 +23834,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-E3BE4A3F5229</t>
         </is>
@@ -23115,7 +23880,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23180,6 +23945,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-7F11850C0654</t>
         </is>

--- a/product_upload/packages/42/file.xlsx
+++ b/product_upload/packages/42/file.xlsx
@@ -1082,8 +1082,16 @@
           <t>8824581240-362-010891505898</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SILOMES 200 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SILOMES 200 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1269,8 +1277,16 @@
           <t>2175390578-785-689954653212</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMALSTYLE forte Lidocaine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DERMALSTYLE forte Lidocaine detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1452,8 +1468,16 @@
           <t>3593079416-179-124723362370</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMALSTYLE smile Lidocaine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DERMALSTYLE smile Lidocaine detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -2423,8 +2447,16 @@
           <t>8090420687-640-260607675381</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAL-C-VITA EFFERVESCENT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CAL-C-VITA EFFERVESCENT detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -3199,8 +3231,16 @@
           <t>3916328872-679-704909500244</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VERTEX</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VERTEX detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -4174,8 +4214,16 @@
           <t>9669747237-550-266056155529</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUPRO 2 mg/24 hrs Transdermal Patches</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NEUPRO 2 mg/24 hrs Transdermal Patches detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4751,8 +4799,16 @@
           <t>4163623619-347-032683910794</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NITYR 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NITYR 5 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5338,8 +5394,16 @@
           <t>8562378693-829-973289023478</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APRELEX 20MCG/ML INHALATION SOLUTION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>APRELEX 20MCG/ML INHALATION SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5525,8 +5589,16 @@
           <t>2598377671-517-145219843410</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADANCOR 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ADANCOR 10 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5720,8 +5792,16 @@
           <t>0977472104-091-779443120536</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ISENTRESS 600MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ISENTRESS 600MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6108,8 +6188,16 @@
           <t>4129654384-769-233648692389</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-OLMEPRESS 20 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CO-OLMEPRESS 20 mg/12.5 mg F.C. Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6494,8 +6582,16 @@
           <t>4093121369-250-834068118472</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NITYR 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NITYR 10 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6876,8 +6972,16 @@
           <t>4573697245-049-641745881256</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMIDIP 20/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>OLMIDIP 20/5 mg FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7067,8 +7171,16 @@
           <t>9283987756-748-817360541206</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMIDIP 40/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>OLMIDIP 40/5 mg FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7258,8 +7370,16 @@
           <t>3646513450-931-912311222988</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMIDIP 40/10 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>OLMIDIP 40/10 mg FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7449,8 +7569,16 @@
           <t>7145347950-866-950747591739</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAMESTA 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DAMESTA 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7636,8 +7764,16 @@
           <t>2570045397-581-569898473467</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAMESTA  20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DAMESTA  20MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8412,8 +8548,16 @@
           <t>9247221606-088-091222552115</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PIRAMYL-MET 2/500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PIRAMYL-MET 2/500 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8603,8 +8747,16 @@
           <t>0694481938-076-736332406154</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIFANCE 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>LIFANCE 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8794,8 +8946,16 @@
           <t>4185433585-544-593517033067</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIFANCE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LIFANCE 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9570,8 +9730,16 @@
           <t>5873875229-940-127254486236</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PAQUIX 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PAQUIX 2.5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -10549,8 +10717,16 @@
           <t>2632710214-802-463277229200</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LANOXIN 0.25MG TAB</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LANOXIN 0.25MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10939,8 +11115,16 @@
           <t>6577081086-807-746379526967</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RECOMBIVAX HB</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>RECOMBIVAX HB detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11128,8 +11312,16 @@
           <t>9841580373-582-486664386214</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RECOMBIVAX HB</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>RECOMBIVAX HB detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11508,8 +11700,16 @@
           <t>0388535921-118-268643411505</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LINDEC 600 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>LINDEC 600 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11695,8 +11895,16 @@
           <t>2533853618-154-579342532918</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORAL SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NIZORAL SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11890,8 +12098,16 @@
           <t>7719291753-985-525197218164</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cuprior</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Cuprior detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12085,8 +12301,16 @@
           <t>2347257711-276-044223007151</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUPRO 8 mg/24 hrs Transdermal Patches</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NEUPRO 8 mg/24 hrs Transdermal Patches detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12268,8 +12492,16 @@
           <t>0066486994-874-763569949121</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GASTROGRAFIN 76-ORAL AQUEOUS SOLN.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>GASTROGRAFIN 76-ORAL AQUEOUS SOLN. detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12459,8 +12691,16 @@
           <t>3590345285-570-048323826069</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUPRO 6 mg/24 hrs Transdermal Patches</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NEUPRO 6 mg/24 hrs Transdermal Patches detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12646,8 +12886,16 @@
           <t>1942959343-446-036876653245</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRONTA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>VIRONTA detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12837,8 +13085,16 @@
           <t>1506497194-634-811533355090</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRONTA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>VIRONTA detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13024,8 +13280,16 @@
           <t>3705754615-335-522145165988</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRONTA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>VIRONTA detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13215,8 +13479,16 @@
           <t>5898555502-106-798199236061</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PEDEXA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>PEDEXA detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13402,8 +13674,16 @@
           <t>1118024532-151-426793281971</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TYRA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TYRA 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13593,8 +13873,16 @@
           <t>1762727316-892-310776737425</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRAVAFEN 40/160 mg</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PRAVAFEN 40/160 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13780,8 +14068,16 @@
           <t>3008126666-148-809809309724</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Kavira</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kavira detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13967,8 +14263,16 @@
           <t>7118438992-282-267958198945</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Kavira</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kavira detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14749,8 +15053,16 @@
           <t>3672845648-118-057495305885</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PecFent 400 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>PecFent 400 MCG NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15334,8 +15646,16 @@
           <t>7337615345-996-449831252038</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RAPAMUNE 1 MG Coated tablet</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>RAPAMUNE 1 MG Coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15521,8 +15841,16 @@
           <t>4404099147-889-103931939810</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TWINZOL EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TWINZOL EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15708,8 +16036,16 @@
           <t>5587787380-471-578145423308</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XIIDRA 50 MG/ML EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>XIIDRA 50 MG/ML EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16096,8 +16432,16 @@
           <t>9878475295-430-939597032336</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PEEVO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PEEVO detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
@@ -16285,8 +16629,16 @@
           <t>8505833365-393-880882160797</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEURITAM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>NEURITAM detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -17041,8 +17393,16 @@
           <t>7137503732-274-901187188628</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORBRENA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>LORBRENA detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17232,8 +17592,16 @@
           <t>1997809021-245-476625265541</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Carglumic Acid Waymade</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Carglumic Acid Waymade detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17423,8 +17791,16 @@
           <t>3671218094-894-316061386209</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Carglumic Acid Waymade</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Carglumic Acid Waymade detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17618,8 +17994,16 @@
           <t>5321336334-263-107302429588</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORBRENA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>LORBRENA detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -19001,8 +19385,16 @@
           <t>8517206391-708-542021697480</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PecFent 400 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>PecFent 400 MCG NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19389,8 +19781,16 @@
           <t>1437415807-731-872984531355</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hyalo4 Plus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Hyalo4 Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19777,8 +20177,16 @@
           <t>0158040977-824-432500476196</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INTRAROSA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>INTRAROSA detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/42/file.xlsx
+++ b/product_upload/packages/42/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22028,7 +22028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22109,40 +22109,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22222,38 +22227,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>114.89</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-5C202FCD1769</t>
         </is>
@@ -22333,38 +22343,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>58.53</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1888F7186BDF</t>
         </is>
@@ -22444,38 +22459,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>55.48</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-1B1DC0DFC601</t>
         </is>
@@ -22555,38 +22575,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>93.95999999999999</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-72DBF593D70C</t>
         </is>
@@ -22666,38 +22691,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>138.05</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-39B4B6256B28</t>
         </is>
@@ -22777,38 +22807,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>416.9</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-EAFEA49F01CD</t>
         </is>
@@ -22888,38 +22923,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>160.97</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-077D984A300A</t>
         </is>
@@ -22999,38 +23039,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>309.43</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-7C9AD9EB502A</t>
         </is>
@@ -23110,38 +23155,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>90.72</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-55FE4599DB71</t>
         </is>
@@ -23221,38 +23271,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>43.05</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-BEED988B89B8</t>
         </is>
@@ -23332,38 +23387,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>394.56</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-AADCB4EA6DAF</t>
         </is>
@@ -23443,38 +23503,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>239.44</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-E221A0B0F398</t>
         </is>
@@ -23554,38 +23619,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>108.2</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-89330BCB3D85</t>
         </is>
@@ -23665,38 +23735,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>42.95</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-E57A416F445D</t>
         </is>
@@ -23776,38 +23851,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>57.43</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-1E0489938352</t>
         </is>
@@ -23887,38 +23967,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>139.35</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-FBE2215685C5</t>
         </is>
@@ -23998,38 +24083,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>390.91</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-46801301C804</t>
         </is>
@@ -24109,38 +24199,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>90.65000000000001</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-1520CA1C9DF9</t>
         </is>
@@ -24220,38 +24315,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>242.41</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-E3BE4A3F5229</t>
         </is>
@@ -24331,38 +24431,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>192.72</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-7F11850C0654</t>
         </is>
